--- a/data.xlsx
+++ b/data.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="204">
   <si>
     <t>Horodatage</t>
   </si>
@@ -388,9 +388,6 @@
     <t>Très apprécié mais cher par rapport au marché du Pet Nat.</t>
   </si>
   <si>
-    <t>Yvain 2</t>
-  </si>
-  <si>
     <t>Arnaud</t>
   </si>
   <si>
@@ -666,6 +663,9 @@
   <si>
     <t>pas dans ma gamme</t>
   </si>
+  <si>
+    <t>Antoine-Alexandre</t>
+  </si>
 </sst>
 </file>
 
@@ -932,6 +932,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="31.38"/>
+    <col customWidth="1" min="2" max="2" width="38.75"/>
     <col customWidth="1" min="3" max="3" width="29.5"/>
     <col customWidth="1" min="4" max="4" width="32.5"/>
     <col customWidth="1" min="9" max="9" width="67.25"/>
@@ -4387,55 +4388,14 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2">
-        <v>46205.37569444445</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E73" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="F73" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="G73" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="H73" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="J73" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="K73" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="L73" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="M73" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="N73" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="O73" s="3">
-        <v>8.0</v>
-      </c>
+      <c r="A73" s="2"/>
     </row>
     <row r="74">
       <c r="A74" s="2">
         <v>46206.70594907407</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>17</v>
@@ -4479,7 +4439,7 @@
         <v>46206.70594907407</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>17</v>
@@ -4523,7 +4483,7 @@
         <v>46206.70594907407</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>17</v>
@@ -4567,7 +4527,7 @@
         <v>46206.70594907407</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>17</v>
@@ -4611,7 +4571,7 @@
         <v>46206.70594907407</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>17</v>
@@ -4655,7 +4615,7 @@
         <v>46206.70594907407</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>17</v>
@@ -4699,7 +4659,7 @@
         <v>46206.70594907407</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>17</v>
@@ -4743,7 +4703,7 @@
         <v>46206.70594907407</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>17</v>
@@ -4787,7 +4747,7 @@
         <v>46206.70594907407</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>17</v>
@@ -4831,7 +4791,7 @@
         <v>46206.70594907407</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>17</v>
@@ -4875,7 +4835,7 @@
         <v>46206.70594907407</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>17</v>
@@ -4919,7 +4879,7 @@
         <v>46206.70594907407</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>17</v>
@@ -4963,7 +4923,7 @@
         <v>46206.70759259259</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>38</v>
@@ -5007,7 +4967,7 @@
         <v>46206.70759259259</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>38</v>
@@ -5051,7 +5011,7 @@
         <v>46206.70759259259</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>38</v>
@@ -5095,7 +5055,7 @@
         <v>46206.70759259259</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>38</v>
@@ -5139,7 +5099,7 @@
         <v>46206.70759259259</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>38</v>
@@ -5183,7 +5143,7 @@
         <v>46206.70759259259</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>38</v>
@@ -5227,7 +5187,7 @@
         <v>46206.71072916667</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>51</v>
@@ -5271,7 +5231,7 @@
         <v>46206.71072916667</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>51</v>
@@ -5315,7 +5275,7 @@
         <v>46206.71072916667</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>51</v>
@@ -5359,7 +5319,7 @@
         <v>46206.71131944445</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>57</v>
@@ -5403,7 +5363,7 @@
         <v>46206.71136574074</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>57</v>
@@ -5447,7 +5407,7 @@
         <v>46206.71240740741</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>59</v>
@@ -5491,7 +5451,7 @@
         <v>46206.71240740741</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>59</v>
@@ -5535,7 +5495,7 @@
         <v>46206.71240740741</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>59</v>
@@ -5579,7 +5539,7 @@
         <v>46209.4419212963</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>64</v>
@@ -5623,7 +5583,7 @@
         <v>46209.4419212963</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>64</v>
@@ -5667,7 +5627,7 @@
         <v>46209.4419212963</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>64</v>
@@ -5711,7 +5671,7 @@
         <v>46209.4419212963</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>64</v>
@@ -5755,7 +5715,7 @@
         <v>46209.58688657408</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>70</v>
@@ -5799,7 +5759,7 @@
         <v>46209.58688657408</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>70</v>
@@ -5843,7 +5803,7 @@
         <v>46209.58688657408</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>70</v>
@@ -5887,7 +5847,7 @@
         <v>46209.58688657408</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>70</v>
@@ -5931,7 +5891,7 @@
         <v>46209.58688657408</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>70</v>
@@ -5975,7 +5935,7 @@
         <v>46209.58688657408</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>70</v>
@@ -6019,7 +5979,7 @@
         <v>46209.58688657408</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>70</v>
@@ -6063,7 +6023,7 @@
         <v>46209.58688657408</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>70</v>
@@ -6107,7 +6067,7 @@
         <v>46209.58688657408</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>70</v>
@@ -6151,7 +6111,7 @@
         <v>46209.58688657408</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>70</v>
@@ -6195,7 +6155,7 @@
         <v>46209.58688657408</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>70</v>
@@ -6239,7 +6199,7 @@
         <v>46209.6550462963</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>87</v>
@@ -6283,7 +6243,7 @@
         <v>46209.6550462963</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>87</v>
@@ -6327,7 +6287,7 @@
         <v>46209.6550462963</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>87</v>
@@ -6371,7 +6331,7 @@
         <v>46209.6550462963</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>87</v>
@@ -6415,7 +6375,7 @@
         <v>46209.6550462963</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>87</v>
@@ -6459,7 +6419,7 @@
         <v>46209.6550462963</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>87</v>
@@ -6503,7 +6463,7 @@
         <v>46209.6550462963</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>87</v>
@@ -6547,7 +6507,7 @@
         <v>46209.6550462963</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>87</v>
@@ -6591,7 +6551,7 @@
         <v>46209.6550462963</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>87</v>
@@ -6635,7 +6595,7 @@
         <v>46209.6550462963</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>87</v>
@@ -6679,7 +6639,7 @@
         <v>46209.6550462963</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>87</v>
@@ -6723,7 +6683,7 @@
         <v>46209.6550462963</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>87</v>
@@ -6767,7 +6727,7 @@
         <v>46209.6550462963</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>87</v>
@@ -6811,7 +6771,7 @@
         <v>46209.655127314814</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>87</v>
@@ -6855,7 +6815,7 @@
         <v>46209.655127314814</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>87</v>
@@ -6899,7 +6859,7 @@
         <v>46209.655127314814</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>87</v>
@@ -6943,7 +6903,7 @@
         <v>46209.655127314814</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>87</v>
@@ -6987,7 +6947,7 @@
         <v>46209.655127314814</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>87</v>
@@ -7031,7 +6991,7 @@
         <v>46209.655127314814</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>87</v>
@@ -7075,7 +7035,7 @@
         <v>46209.655127314814</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>87</v>
@@ -7119,7 +7079,7 @@
         <v>46209.655127314814</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>87</v>
@@ -7163,7 +7123,7 @@
         <v>46209.655127314814</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>87</v>
@@ -7207,7 +7167,7 @@
         <v>46209.655127314814</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>87</v>
@@ -7251,7 +7211,7 @@
         <v>46209.655127314814</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>87</v>
@@ -7295,7 +7255,7 @@
         <v>46209.655127314814</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>87</v>
@@ -7339,7 +7299,7 @@
         <v>46209.655127314814</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>87</v>
@@ -7383,7 +7343,7 @@
         <v>46209.658055555556</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>106</v>
@@ -7427,7 +7387,7 @@
         <v>46209.658055555556</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>106</v>
@@ -7471,7 +7431,7 @@
         <v>46209.658055555556</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>106</v>
@@ -7515,7 +7475,7 @@
         <v>46209.658055555556</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>106</v>
@@ -7559,7 +7519,7 @@
         <v>46209.658055555556</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>106</v>
@@ -7603,7 +7563,7 @@
         <v>46209.658055555556</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>106</v>
@@ -7647,7 +7607,7 @@
         <v>46209.658055555556</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>106</v>
@@ -7691,7 +7651,7 @@
         <v>46209.658055555556</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>106</v>
@@ -7735,7 +7695,7 @@
         <v>46209.658055555556</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>106</v>
@@ -7779,7 +7739,7 @@
         <v>46209.658055555556</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>106</v>
@@ -7823,7 +7783,7 @@
         <v>46209.658055555556</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>106</v>
@@ -7867,7 +7827,7 @@
         <v>46209.658055555556</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>106</v>
@@ -7911,7 +7871,7 @@
         <v>46209.658055555556</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>106</v>
@@ -7955,7 +7915,7 @@
         <v>46209.658055555556</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>106</v>
@@ -7999,7 +7959,7 @@
         <v>46209.658055555556</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>106</v>
@@ -8043,7 +8003,7 @@
         <v>46209.65856481482</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>62</v>
@@ -8087,7 +8047,7 @@
         <v>46209.659004629626</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>103</v>
@@ -8131,7 +8091,7 @@
         <v>46209.659004629626</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>103</v>
@@ -8175,7 +8135,7 @@
         <v>46209.6590625</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>103</v>
@@ -8219,7 +8179,7 @@
         <v>46209.6590625</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>103</v>
@@ -8263,7 +8223,7 @@
         <v>46210.458958333336</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>17</v>
@@ -8284,28 +8244,28 @@
         <v>6.0</v>
       </c>
       <c r="I161" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J161" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="K161" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="L161" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="M161" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N161" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="O161" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P161" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="J161" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="K161" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="L161" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="M161" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="N161" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="O161" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P161" s="1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="162">
@@ -8313,7 +8273,7 @@
         <v>46210.458958333336</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>17</v>
@@ -8334,7 +8294,7 @@
         <v>8.0</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J162" s="3">
         <v>9.0</v>
@@ -8355,7 +8315,7 @@
         <v>10.0</v>
       </c>
       <c r="P162" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="163">
@@ -8363,7 +8323,7 @@
         <v>46210.458958333336</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>17</v>
@@ -8384,7 +8344,7 @@
         <v>8.0</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J163" s="3">
         <v>9.0</v>
@@ -8405,7 +8365,7 @@
         <v>10.0</v>
       </c>
       <c r="P163" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="164">
@@ -8413,7 +8373,7 @@
         <v>46210.458958333336</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>17</v>
@@ -8434,7 +8394,7 @@
         <v>5.0</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J164" s="3">
         <v>9.0</v>
@@ -8455,7 +8415,7 @@
         <v>10.0</v>
       </c>
       <c r="P164" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="165">
@@ -8463,7 +8423,7 @@
         <v>46210.458958333336</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>17</v>
@@ -8484,7 +8444,7 @@
         <v>5.0</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J165" s="3">
         <v>9.0</v>
@@ -8505,7 +8465,7 @@
         <v>10.0</v>
       </c>
       <c r="P165" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="166">
@@ -8513,7 +8473,7 @@
         <v>46210.458958333336</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>17</v>
@@ -8534,7 +8494,7 @@
         <v>7.0</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J166" s="3">
         <v>9.0</v>
@@ -8555,7 +8515,7 @@
         <v>10.0</v>
       </c>
       <c r="P166" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="167">
@@ -8563,7 +8523,7 @@
         <v>46210.458958333336</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>17</v>
@@ -8584,7 +8544,7 @@
         <v>10.0</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J167" s="3">
         <v>9.0</v>
@@ -8605,7 +8565,7 @@
         <v>10.0</v>
       </c>
       <c r="P167" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="168">
@@ -8613,7 +8573,7 @@
         <v>46210.458958333336</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>17</v>
@@ -8634,7 +8594,7 @@
         <v>6.0</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J168" s="3">
         <v>9.0</v>
@@ -8655,7 +8615,7 @@
         <v>10.0</v>
       </c>
       <c r="P168" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="169">
@@ -8663,7 +8623,7 @@
         <v>46210.458958333336</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>17</v>
@@ -8684,7 +8644,7 @@
         <v>7.0</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J169" s="3">
         <v>9.0</v>
@@ -8705,7 +8665,7 @@
         <v>10.0</v>
       </c>
       <c r="P169" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="170">
@@ -8713,7 +8673,7 @@
         <v>46210.458958333336</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>17</v>
@@ -8734,7 +8694,7 @@
         <v>6.0</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J170" s="3">
         <v>9.0</v>
@@ -8755,7 +8715,7 @@
         <v>10.0</v>
       </c>
       <c r="P170" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="171">
@@ -8763,7 +8723,7 @@
         <v>46210.458958333336</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>17</v>
@@ -8784,7 +8744,7 @@
         <v>10.0</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J171" s="3">
         <v>9.0</v>
@@ -8805,7 +8765,7 @@
         <v>10.0</v>
       </c>
       <c r="P171" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="172">
@@ -8813,7 +8773,7 @@
         <v>46210.458958333336</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>17</v>
@@ -8834,7 +8794,7 @@
         <v>10.0</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J172" s="3">
         <v>9.0</v>
@@ -8855,7 +8815,7 @@
         <v>10.0</v>
       </c>
       <c r="P172" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="173">
@@ -8863,7 +8823,7 @@
         <v>46210.4628125</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>38</v>
@@ -8884,7 +8844,7 @@
         <v>8.0</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J173" s="3">
         <v>6.0</v>
@@ -8905,7 +8865,7 @@
         <v>5.0</v>
       </c>
       <c r="P173" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="174">
@@ -8913,7 +8873,7 @@
         <v>46210.4628125</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>38</v>
@@ -8934,7 +8894,7 @@
         <v>6.0</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J174" s="3">
         <v>6.0</v>
@@ -8955,7 +8915,7 @@
         <v>5.0</v>
       </c>
       <c r="P174" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="175">
@@ -8963,7 +8923,7 @@
         <v>46210.4628125</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>38</v>
@@ -8984,7 +8944,7 @@
         <v>7.0</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J175" s="3">
         <v>6.0</v>
@@ -9005,7 +8965,7 @@
         <v>5.0</v>
       </c>
       <c r="P175" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="176">
@@ -9013,7 +8973,7 @@
         <v>46210.4628125</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>38</v>
@@ -9052,7 +9012,7 @@
         <v>5.0</v>
       </c>
       <c r="P176" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="177">
@@ -9060,7 +9020,7 @@
         <v>46210.4628125</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>38</v>
@@ -9081,7 +9041,7 @@
         <v>8.0</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J177" s="3">
         <v>6.0</v>
@@ -9102,7 +9062,7 @@
         <v>5.0</v>
       </c>
       <c r="P177" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="178">
@@ -9110,7 +9070,7 @@
         <v>46210.4628125</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>38</v>
@@ -9131,7 +9091,7 @@
         <v>9.0</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J178" s="3">
         <v>6.0</v>
@@ -9152,7 +9112,7 @@
         <v>5.0</v>
       </c>
       <c r="P178" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="179">
@@ -9160,7 +9120,7 @@
         <v>46210.464224537034</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>59</v>
@@ -9181,7 +9141,7 @@
         <v>9.0</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J179" s="3">
         <v>8.0</v>
@@ -9202,7 +9162,7 @@
         <v>10.0</v>
       </c>
       <c r="P179" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="180">
@@ -9210,7 +9170,7 @@
         <v>46210.464224537034</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>59</v>
@@ -9249,7 +9209,7 @@
         <v>10.0</v>
       </c>
       <c r="P180" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="181">
@@ -9257,7 +9217,7 @@
         <v>46210.464224537034</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>59</v>
@@ -9278,7 +9238,7 @@
         <v>9.0</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J181" s="3">
         <v>8.0</v>
@@ -9299,7 +9259,7 @@
         <v>10.0</v>
       </c>
       <c r="P181" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="182">
@@ -9307,7 +9267,7 @@
         <v>46210.47243055556</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>57</v>
@@ -9328,7 +9288,7 @@
         <v>5.0</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J182" s="3">
         <v>9.0</v>
@@ -9354,7 +9314,7 @@
         <v>46210.47824074074</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>51</v>
@@ -9393,7 +9353,7 @@
         <v>6.0</v>
       </c>
       <c r="P183" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="184">
@@ -9401,7 +9361,7 @@
         <v>46210.47824074074</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>51</v>
@@ -9422,7 +9382,7 @@
         <v>10.0</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J184" s="3">
         <v>9.0</v>
@@ -9443,7 +9403,7 @@
         <v>6.0</v>
       </c>
       <c r="P184" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="185">
@@ -9451,7 +9411,7 @@
         <v>46210.47824074074</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>51</v>
@@ -9472,7 +9432,7 @@
         <v>6.0</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J185" s="3">
         <v>9.0</v>
@@ -9493,7 +9453,7 @@
         <v>6.0</v>
       </c>
       <c r="P185" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="186">
@@ -9501,7 +9461,7 @@
         <v>46210.47907407407</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>62</v>
@@ -9540,7 +9500,7 @@
         <v>7.0</v>
       </c>
       <c r="P186" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="187">
@@ -9548,7 +9508,7 @@
         <v>46210.483761574076</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>103</v>
@@ -9587,7 +9547,7 @@
         <v>3.0</v>
       </c>
       <c r="P187" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="188">
@@ -9595,7 +9555,7 @@
         <v>46210.483761574076</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>103</v>
@@ -9616,7 +9576,7 @@
         <v>3.0</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J188" s="3">
         <v>5.0</v>
@@ -9637,7 +9597,7 @@
         <v>3.0</v>
       </c>
       <c r="P188" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="189">
@@ -9645,7 +9605,7 @@
         <v>46210.49482638889</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>70</v>
@@ -9666,7 +9626,7 @@
         <v>10.0</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J189" s="3">
         <v>3.0</v>
@@ -9687,7 +9647,7 @@
         <v>8.0</v>
       </c>
       <c r="P189" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="190">
@@ -9695,7 +9655,7 @@
         <v>46210.49482638889</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>70</v>
@@ -9716,7 +9676,7 @@
         <v>9.0</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J190" s="3">
         <v>3.0</v>
@@ -9737,7 +9697,7 @@
         <v>8.0</v>
       </c>
       <c r="P190" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="191">
@@ -9745,7 +9705,7 @@
         <v>46210.49482638889</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>70</v>
@@ -9766,7 +9726,7 @@
         <v>7.0</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J191" s="3">
         <v>3.0</v>
@@ -9787,7 +9747,7 @@
         <v>8.0</v>
       </c>
       <c r="P191" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="192">
@@ -9795,7 +9755,7 @@
         <v>46210.49482638889</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>70</v>
@@ -9816,7 +9776,7 @@
         <v>8.0</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J192" s="3">
         <v>3.0</v>
@@ -9837,7 +9797,7 @@
         <v>8.0</v>
       </c>
       <c r="P192" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="193">
@@ -9845,7 +9805,7 @@
         <v>46210.49482638889</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>70</v>
@@ -9866,7 +9826,7 @@
         <v>8.0</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J193" s="3">
         <v>3.0</v>
@@ -9887,7 +9847,7 @@
         <v>8.0</v>
       </c>
       <c r="P193" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="194">
@@ -9895,7 +9855,7 @@
         <v>46210.49482638889</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>70</v>
@@ -9916,7 +9876,7 @@
         <v>8.0</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J194" s="3">
         <v>3.0</v>
@@ -9937,7 +9897,7 @@
         <v>8.0</v>
       </c>
       <c r="P194" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="195">
@@ -9945,7 +9905,7 @@
         <v>46210.49482638889</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>70</v>
@@ -9966,7 +9926,7 @@
         <v>8.0</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J195" s="3">
         <v>3.0</v>
@@ -9987,7 +9947,7 @@
         <v>8.0</v>
       </c>
       <c r="P195" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="196">
@@ -9995,7 +9955,7 @@
         <v>46210.49482638889</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>70</v>
@@ -10016,7 +9976,7 @@
         <v>7.0</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J196" s="3">
         <v>3.0</v>
@@ -10037,7 +9997,7 @@
         <v>8.0</v>
       </c>
       <c r="P196" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="197">
@@ -10045,7 +10005,7 @@
         <v>46210.49482638889</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>70</v>
@@ -10066,7 +10026,7 @@
         <v>7.0</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J197" s="3">
         <v>3.0</v>
@@ -10087,7 +10047,7 @@
         <v>8.0</v>
       </c>
       <c r="P197" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="198">
@@ -10095,7 +10055,7 @@
         <v>46210.49482638889</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>70</v>
@@ -10116,7 +10076,7 @@
         <v>8.0</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J198" s="3">
         <v>3.0</v>
@@ -10137,7 +10097,7 @@
         <v>8.0</v>
       </c>
       <c r="P198" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="199">
@@ -10145,7 +10105,7 @@
         <v>46210.49482638889</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>70</v>
@@ -10166,7 +10126,7 @@
         <v>10.0</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J199" s="3">
         <v>3.0</v>
@@ -10187,7 +10147,7 @@
         <v>8.0</v>
       </c>
       <c r="P199" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="200">
@@ -10195,7 +10155,7 @@
         <v>46210.49851851852</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>87</v>
@@ -10216,28 +10176,28 @@
         <v>10.0</v>
       </c>
       <c r="I200" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J200" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="K200" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="L200" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="M200" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="N200" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="O200" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P200" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="J200" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="K200" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="L200" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="M200" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="N200" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="O200" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P200" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="201">
@@ -10245,7 +10205,7 @@
         <v>46210.49851851852</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>87</v>
@@ -10284,7 +10244,7 @@
         <v>10.0</v>
       </c>
       <c r="P201" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="202">
@@ -10292,7 +10252,7 @@
         <v>46210.49851851852</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>87</v>
@@ -10313,7 +10273,7 @@
         <v>9.0</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J202" s="3">
         <v>10.0</v>
@@ -10334,7 +10294,7 @@
         <v>10.0</v>
       </c>
       <c r="P202" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="203">
@@ -10342,7 +10302,7 @@
         <v>46210.49851851852</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>87</v>
@@ -10363,7 +10323,7 @@
         <v>10.0</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J203" s="3">
         <v>10.0</v>
@@ -10384,7 +10344,7 @@
         <v>10.0</v>
       </c>
       <c r="P203" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="204">
@@ -10392,7 +10352,7 @@
         <v>46210.49851851852</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>87</v>
@@ -10413,7 +10373,7 @@
         <v>9.0</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J204" s="3">
         <v>10.0</v>
@@ -10434,7 +10394,7 @@
         <v>10.0</v>
       </c>
       <c r="P204" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="205">
@@ -10442,7 +10402,7 @@
         <v>46210.49851851852</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>87</v>
@@ -10463,7 +10423,7 @@
         <v>10.0</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J205" s="3">
         <v>10.0</v>
@@ -10484,7 +10444,7 @@
         <v>10.0</v>
       </c>
       <c r="P205" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="206">
@@ -10492,7 +10452,7 @@
         <v>46210.49851851852</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>87</v>
@@ -10513,7 +10473,7 @@
         <v>10.0</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J206" s="3">
         <v>10.0</v>
@@ -10534,7 +10494,7 @@
         <v>10.0</v>
       </c>
       <c r="P206" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="207">
@@ -10542,7 +10502,7 @@
         <v>46210.49851851852</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>87</v>
@@ -10563,7 +10523,7 @@
         <v>5.0</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J207" s="3">
         <v>10.0</v>
@@ -10584,7 +10544,7 @@
         <v>10.0</v>
       </c>
       <c r="P207" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="208">
@@ -10592,7 +10552,7 @@
         <v>46210.49851851852</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>87</v>
@@ -10613,7 +10573,7 @@
         <v>9.0</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J208" s="3">
         <v>10.0</v>
@@ -10634,7 +10594,7 @@
         <v>10.0</v>
       </c>
       <c r="P208" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="209">
@@ -10642,7 +10602,7 @@
         <v>46210.49851851852</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>87</v>
@@ -10681,7 +10641,7 @@
         <v>10.0</v>
       </c>
       <c r="P209" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="210">
@@ -10689,7 +10649,7 @@
         <v>46210.49851851852</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>87</v>
@@ -10710,7 +10670,7 @@
         <v>8.0</v>
       </c>
       <c r="I210" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J210" s="3">
         <v>10.0</v>
@@ -10731,7 +10691,7 @@
         <v>10.0</v>
       </c>
       <c r="P210" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="211">
@@ -10739,7 +10699,7 @@
         <v>46210.49851851852</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>87</v>
@@ -10778,7 +10738,7 @@
         <v>10.0</v>
       </c>
       <c r="P211" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="212">
@@ -10786,7 +10746,7 @@
         <v>46210.49851851852</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>87</v>
@@ -10825,7 +10785,7 @@
         <v>10.0</v>
       </c>
       <c r="P212" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="213">
@@ -10833,7 +10793,7 @@
         <v>46210.502384259256</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>106</v>
@@ -10854,7 +10814,7 @@
         <v>10.0</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J213" s="3">
         <v>5.0</v>
@@ -10875,7 +10835,7 @@
         <v>9.0</v>
       </c>
       <c r="P213" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="214">
@@ -10883,7 +10843,7 @@
         <v>46210.502384259256</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>106</v>
@@ -10904,7 +10864,7 @@
         <v>10.0</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J214" s="3">
         <v>5.0</v>
@@ -10925,7 +10885,7 @@
         <v>9.0</v>
       </c>
       <c r="P214" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="215">
@@ -10933,7 +10893,7 @@
         <v>46210.502384259256</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>106</v>
@@ -10972,7 +10932,7 @@
         <v>9.0</v>
       </c>
       <c r="P215" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="216">
@@ -10980,7 +10940,7 @@
         <v>46210.502384259256</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>106</v>
@@ -11001,7 +10961,7 @@
         <v>10.0</v>
       </c>
       <c r="I216" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J216" s="3">
         <v>5.0</v>
@@ -11022,7 +10982,7 @@
         <v>9.0</v>
       </c>
       <c r="P216" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="217">
@@ -11030,7 +10990,7 @@
         <v>46210.502384259256</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>106</v>
@@ -11051,7 +11011,7 @@
         <v>10.0</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J217" s="3">
         <v>5.0</v>
@@ -11072,7 +11032,7 @@
         <v>9.0</v>
       </c>
       <c r="P217" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="218">
@@ -11080,7 +11040,7 @@
         <v>46210.502384259256</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>106</v>
@@ -11101,7 +11061,7 @@
         <v>9.0</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J218" s="3">
         <v>5.0</v>
@@ -11122,7 +11082,7 @@
         <v>9.0</v>
       </c>
       <c r="P218" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="219">
@@ -11130,7 +11090,7 @@
         <v>46210.502384259256</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>106</v>
@@ -11169,7 +11129,7 @@
         <v>9.0</v>
       </c>
       <c r="P219" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="220">
@@ -11177,7 +11137,7 @@
         <v>46210.502384259256</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>106</v>
@@ -11198,7 +11158,7 @@
         <v>5.0</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J220" s="3">
         <v>5.0</v>
@@ -11219,7 +11179,7 @@
         <v>9.0</v>
       </c>
       <c r="P220" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="221">
@@ -11227,7 +11187,7 @@
         <v>46210.502384259256</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>106</v>
@@ -11248,7 +11208,7 @@
         <v>7.0</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J221" s="3">
         <v>5.0</v>
@@ -11269,7 +11229,7 @@
         <v>9.0</v>
       </c>
       <c r="P221" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="222">
@@ -11277,7 +11237,7 @@
         <v>46210.502384259256</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>106</v>
@@ -11298,7 +11258,7 @@
         <v>9.0</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J222" s="3">
         <v>5.0</v>
@@ -11319,7 +11279,7 @@
         <v>9.0</v>
       </c>
       <c r="P222" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="223">
@@ -11327,7 +11287,7 @@
         <v>46210.502384259256</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>106</v>
@@ -11348,7 +11308,7 @@
         <v>3.0</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J223" s="3">
         <v>5.0</v>
@@ -11369,7 +11329,7 @@
         <v>9.0</v>
       </c>
       <c r="P223" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="224">
@@ -11377,7 +11337,7 @@
         <v>46210.502384259256</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>106</v>
@@ -11416,7 +11376,7 @@
         <v>9.0</v>
       </c>
       <c r="P224" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="225">
@@ -11424,7 +11384,7 @@
         <v>46210.502384259256</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>106</v>
@@ -11463,7 +11423,7 @@
         <v>9.0</v>
       </c>
       <c r="P225" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="226">
@@ -11471,7 +11431,7 @@
         <v>46210.502384259256</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>106</v>
@@ -11492,7 +11452,7 @@
         <v>10.0</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J226" s="3">
         <v>5.0</v>
@@ -11513,7 +11473,7 @@
         <v>9.0</v>
       </c>
       <c r="P226" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="227">
@@ -11521,7 +11481,7 @@
         <v>46210.502384259256</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>106</v>
@@ -11542,7 +11502,7 @@
         <v>3.0</v>
       </c>
       <c r="I227" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J227" s="3">
         <v>5.0</v>
@@ -11563,7 +11523,7 @@
         <v>9.0</v>
       </c>
       <c r="P227" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="228">
@@ -11571,7 +11531,7 @@
         <v>46211.76648148148</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>17</v>
@@ -11615,7 +11575,7 @@
         <v>46211.76648148148</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>17</v>
@@ -11659,7 +11619,7 @@
         <v>46211.76648148148</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>17</v>
@@ -11703,7 +11663,7 @@
         <v>46211.76648148148</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>17</v>
@@ -11747,7 +11707,7 @@
         <v>46211.76648148148</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>17</v>
@@ -11791,7 +11751,7 @@
         <v>46211.76648148148</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>17</v>
@@ -11835,7 +11795,7 @@
         <v>46211.76648148148</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>17</v>
@@ -11879,7 +11839,7 @@
         <v>46211.76648148148</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>17</v>
@@ -11923,7 +11883,7 @@
         <v>46211.76648148148</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>17</v>
@@ -11967,7 +11927,7 @@
         <v>46211.76648148148</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>17</v>
@@ -12011,7 +11971,7 @@
         <v>46211.76648148148</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>17</v>
@@ -12043,7 +12003,7 @@
         <v>46211.76648148148</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>17</v>
@@ -12075,7 +12035,7 @@
         <v>46211.76762731482</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>38</v>
@@ -12119,7 +12079,7 @@
         <v>46211.76762731482</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>38</v>
@@ -12163,7 +12123,7 @@
         <v>46211.76762731482</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>38</v>
@@ -12207,7 +12167,7 @@
         <v>46211.76762731482</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>38</v>
@@ -12251,7 +12211,7 @@
         <v>46211.76762731482</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>38</v>
@@ -12283,7 +12243,7 @@
         <v>46211.76762731482</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>38</v>
@@ -12315,7 +12275,7 @@
         <v>46211.76849537037</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>51</v>
@@ -12359,7 +12319,7 @@
         <v>46211.76849537037</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>51</v>
@@ -12403,7 +12363,7 @@
         <v>46211.76849537037</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>51</v>
@@ -12447,7 +12407,7 @@
         <v>46211.76923611111</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>57</v>
@@ -12491,7 +12451,7 @@
         <v>46211.76969907407</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>59</v>
@@ -12523,7 +12483,7 @@
         <v>46211.76969907407</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>59</v>
@@ -12555,7 +12515,7 @@
         <v>46211.76969907407</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>59</v>
@@ -12587,7 +12547,7 @@
         <v>46211.7700462963</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>62</v>
@@ -12619,7 +12579,7 @@
         <v>46211.77128472222</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>64</v>
@@ -12663,7 +12623,7 @@
         <v>46211.77128472222</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>64</v>
@@ -12707,7 +12667,7 @@
         <v>46211.77128472222</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>64</v>
@@ -12751,7 +12711,7 @@
         <v>46211.77128472222</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>64</v>
@@ -12783,7 +12743,7 @@
         <v>46211.77315972222</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>70</v>
@@ -12827,7 +12787,7 @@
         <v>46211.77315972222</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>70</v>
@@ -12871,7 +12831,7 @@
         <v>46211.77315972222</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>70</v>
@@ -12915,7 +12875,7 @@
         <v>46211.77315972222</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>70</v>
@@ -12959,7 +12919,7 @@
         <v>46211.77315972222</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>70</v>
@@ -13003,7 +12963,7 @@
         <v>46211.77315972222</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>70</v>
@@ -13047,7 +13007,7 @@
         <v>46211.77315972222</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>70</v>
@@ -13079,7 +13039,7 @@
         <v>46211.77315972222</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>70</v>
@@ -13123,7 +13083,7 @@
         <v>46211.77315972222</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>70</v>
@@ -13167,7 +13127,7 @@
         <v>46211.77315972222</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>70</v>
@@ -13199,7 +13159,7 @@
         <v>46211.77315972222</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>70</v>
@@ -13231,7 +13191,7 @@
         <v>46211.77521990741</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>87</v>
@@ -13275,7 +13235,7 @@
         <v>46211.77521990741</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>87</v>
@@ -13319,7 +13279,7 @@
         <v>46211.77521990741</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>87</v>
@@ -13363,7 +13323,7 @@
         <v>46211.77521990741</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>87</v>
@@ -13407,7 +13367,7 @@
         <v>46211.77521990741</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>87</v>
@@ -13451,7 +13411,7 @@
         <v>46211.77521990741</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>87</v>
@@ -13495,7 +13455,7 @@
         <v>46211.77521990741</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>87</v>
@@ -13527,7 +13487,7 @@
         <v>46211.77521990741</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>87</v>
@@ -13559,7 +13519,7 @@
         <v>46211.77521990741</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>87</v>
@@ -13591,7 +13551,7 @@
         <v>46211.77521990741</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>87</v>
@@ -13635,7 +13595,7 @@
         <v>46211.77521990741</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>87</v>
@@ -13679,7 +13639,7 @@
         <v>46211.77521990741</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>87</v>
@@ -13723,7 +13683,7 @@
         <v>46211.77521990741</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>87</v>
@@ -13767,7 +13727,7 @@
         <v>46211.776979166665</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>106</v>
@@ -13811,7 +13771,7 @@
         <v>46211.776979166665</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>106</v>
@@ -13855,7 +13815,7 @@
         <v>46211.776979166665</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>106</v>
@@ -13899,7 +13859,7 @@
         <v>46211.776979166665</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>106</v>
@@ -13943,7 +13903,7 @@
         <v>46211.776979166665</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>106</v>
@@ -13987,7 +13947,7 @@
         <v>46211.776979166665</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>106</v>
@@ -14031,7 +13991,7 @@
         <v>46211.776979166665</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>106</v>
@@ -14075,7 +14035,7 @@
         <v>46211.776979166665</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>106</v>
@@ -14107,7 +14067,7 @@
         <v>46211.776979166665</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>106</v>
@@ -14139,7 +14099,7 @@
         <v>46211.776979166665</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>106</v>
@@ -14183,7 +14143,7 @@
         <v>46211.776979166665</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>106</v>
@@ -14215,7 +14175,7 @@
         <v>46211.776979166665</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>106</v>
@@ -14247,7 +14207,7 @@
         <v>46211.776979166665</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>106</v>
@@ -14279,7 +14239,7 @@
         <v>46211.776979166665</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>106</v>
@@ -14311,7 +14271,7 @@
         <v>46211.776979166665</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>106</v>
@@ -14343,7 +14303,7 @@
         <v>46211.77737268519</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>103</v>
@@ -14375,7 +14335,7 @@
         <v>46211.77737268519</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>103</v>
@@ -14407,7 +14367,7 @@
         <v>46212.51012731482</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>17</v>
@@ -14428,7 +14388,7 @@
         <v>7.0</v>
       </c>
       <c r="I299" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J299" s="3">
         <v>4.0</v>
@@ -14449,7 +14409,7 @@
         <v>8.0</v>
       </c>
       <c r="P299" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="300">
@@ -14457,7 +14417,7 @@
         <v>46212.51012731482</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>17</v>
@@ -14478,7 +14438,7 @@
         <v>8.0</v>
       </c>
       <c r="I300" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J300" s="3">
         <v>4.0</v>
@@ -14499,7 +14459,7 @@
         <v>8.0</v>
       </c>
       <c r="P300" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="301">
@@ -14507,7 +14467,7 @@
         <v>46212.51012731482</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>17</v>
@@ -14528,7 +14488,7 @@
         <v>5.0</v>
       </c>
       <c r="I301" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J301" s="3">
         <v>4.0</v>
@@ -14549,7 +14509,7 @@
         <v>8.0</v>
       </c>
       <c r="P301" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="302">
@@ -14557,7 +14517,7 @@
         <v>46212.51012731482</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>17</v>
@@ -14596,7 +14556,7 @@
         <v>8.0</v>
       </c>
       <c r="P302" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="303">
@@ -14604,7 +14564,7 @@
         <v>46212.51012731482</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>17</v>
@@ -14625,7 +14585,7 @@
         <v>7.0</v>
       </c>
       <c r="I303" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J303" s="3">
         <v>4.0</v>
@@ -14646,7 +14606,7 @@
         <v>8.0</v>
       </c>
       <c r="P303" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="304">
@@ -14654,7 +14614,7 @@
         <v>46212.51012731482</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>17</v>
@@ -14693,7 +14653,7 @@
         <v>8.0</v>
       </c>
       <c r="P304" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="305">
@@ -14701,7 +14661,7 @@
         <v>46212.51012731482</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>17</v>
@@ -14722,7 +14682,7 @@
         <v>7.0</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J305" s="3">
         <v>4.0</v>
@@ -14743,7 +14703,7 @@
         <v>8.0</v>
       </c>
       <c r="P305" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="306">
@@ -14751,7 +14711,7 @@
         <v>46212.51012731482</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>17</v>
@@ -14790,7 +14750,7 @@
         <v>8.0</v>
       </c>
       <c r="P306" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="307">
@@ -14798,7 +14758,7 @@
         <v>46212.51012731482</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>17</v>
@@ -14819,7 +14779,7 @@
         <v>7.0</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J307" s="3">
         <v>4.0</v>
@@ -14840,7 +14800,7 @@
         <v>8.0</v>
       </c>
       <c r="P307" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="308">
@@ -14848,7 +14808,7 @@
         <v>46212.51012731482</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>17</v>
@@ -14887,7 +14847,7 @@
         <v>8.0</v>
       </c>
       <c r="P308" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="309">
@@ -14895,7 +14855,7 @@
         <v>46212.51012731482</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>17</v>
@@ -14934,7 +14894,7 @@
         <v>8.0</v>
       </c>
       <c r="P309" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="310">
@@ -14942,7 +14902,7 @@
         <v>46212.51012731482</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>17</v>
@@ -14981,7 +14941,7 @@
         <v>8.0</v>
       </c>
       <c r="P310" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="311">
@@ -14989,7 +14949,7 @@
         <v>46212.519155092596</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>38</v>
@@ -15028,7 +14988,7 @@
         <v>7.0</v>
       </c>
       <c r="P311" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="312">
@@ -15036,7 +14996,7 @@
         <v>46212.519155092596</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>38</v>
@@ -15075,7 +15035,7 @@
         <v>7.0</v>
       </c>
       <c r="P312" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="313">
@@ -15083,7 +15043,7 @@
         <v>46212.519155092596</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>38</v>
@@ -15122,7 +15082,7 @@
         <v>7.0</v>
       </c>
       <c r="P313" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="314">
@@ -15130,7 +15090,7 @@
         <v>46212.519155092596</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>38</v>
@@ -15169,7 +15129,7 @@
         <v>7.0</v>
       </c>
       <c r="P314" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="315">
@@ -15177,7 +15137,7 @@
         <v>46212.519155092596</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>38</v>
@@ -15198,7 +15158,7 @@
         <v>5.0</v>
       </c>
       <c r="I315" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J315" s="3">
         <v>8.0</v>
@@ -15219,7 +15179,7 @@
         <v>7.0</v>
       </c>
       <c r="P315" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="316">
@@ -15227,7 +15187,7 @@
         <v>46212.519155092596</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>38</v>
@@ -15266,7 +15226,7 @@
         <v>7.0</v>
       </c>
       <c r="P316" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="317">
@@ -15274,7 +15234,7 @@
         <v>46212.52190972222</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>51</v>
@@ -15318,7 +15278,7 @@
         <v>46212.52190972222</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>51</v>
@@ -15362,7 +15322,7 @@
         <v>46212.52190972222</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>51</v>
@@ -15383,7 +15343,7 @@
         <v>6.0</v>
       </c>
       <c r="I319" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J319" s="3">
         <v>4.0</v>
@@ -15409,7 +15369,7 @@
         <v>46212.52290509259</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>57</v>
@@ -15453,7 +15413,7 @@
         <v>46212.52357638889</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>62</v>
@@ -15497,7 +15457,7 @@
         <v>46213.7478125</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>64</v>
@@ -15541,7 +15501,7 @@
         <v>46213.7478125</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>64</v>
@@ -15585,7 +15545,7 @@
         <v>46213.7478125</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>64</v>
@@ -15629,7 +15589,7 @@
         <v>46213.7478125</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>64</v>
@@ -15650,7 +15610,7 @@
         <v>5.0</v>
       </c>
       <c r="I325" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J325" s="3">
         <v>7.0</v>
@@ -15676,7 +15636,7 @@
         <v>46213.75188657407</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>70</v>
@@ -15720,7 +15680,7 @@
         <v>46213.75188657407</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>70</v>
@@ -15764,7 +15724,7 @@
         <v>46213.75188657407</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>70</v>
@@ -15808,7 +15768,7 @@
         <v>46213.75188657407</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>70</v>
@@ -15852,7 +15812,7 @@
         <v>46213.75188657407</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>70</v>
@@ -15896,7 +15856,7 @@
         <v>46213.75188657407</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>70</v>
@@ -15940,7 +15900,7 @@
         <v>46213.75188657407</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>70</v>
@@ -15984,7 +15944,7 @@
         <v>46213.75188657407</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>70</v>
@@ -16028,7 +15988,7 @@
         <v>46213.75188657407</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>70</v>
@@ -16072,7 +16032,7 @@
         <v>46213.75188657407</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>70</v>
@@ -16116,7 +16076,7 @@
         <v>46213.75188657407</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>70</v>
@@ -16160,7 +16120,7 @@
         <v>46213.75586805555</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>87</v>
@@ -16204,7 +16164,7 @@
         <v>46213.75586805555</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>87</v>
@@ -16248,7 +16208,7 @@
         <v>46213.75586805555</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>87</v>
@@ -16292,7 +16252,7 @@
         <v>46213.75586805555</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>87</v>
@@ -16336,7 +16296,7 @@
         <v>46213.75586805555</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>87</v>
@@ -16380,7 +16340,7 @@
         <v>46213.75586805555</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>87</v>
@@ -16424,7 +16384,7 @@
         <v>46213.75586805555</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>87</v>
@@ -16468,7 +16428,7 @@
         <v>46213.75586805555</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>87</v>
@@ -16512,7 +16472,7 @@
         <v>46213.75586805555</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>87</v>
@@ -16556,7 +16516,7 @@
         <v>46213.75586805555</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>87</v>
@@ -16600,7 +16560,7 @@
         <v>46213.75586805555</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>87</v>
@@ -16644,7 +16604,7 @@
         <v>46213.75586805555</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>87</v>
@@ -16688,7 +16648,7 @@
         <v>46213.75586805555</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>87</v>
@@ -16732,7 +16692,7 @@
         <v>46213.75945601852</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>106</v>
@@ -16776,7 +16736,7 @@
         <v>46213.75945601852</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>106</v>
@@ -16820,7 +16780,7 @@
         <v>46213.75945601852</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>106</v>
@@ -16864,7 +16824,7 @@
         <v>46213.75945601852</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>106</v>
@@ -16908,7 +16868,7 @@
         <v>46213.75945601852</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>106</v>
@@ -16952,7 +16912,7 @@
         <v>46213.75945601852</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>106</v>
@@ -16996,7 +16956,7 @@
         <v>46213.75945601852</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>106</v>
@@ -17040,7 +17000,7 @@
         <v>46213.75945601852</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>106</v>
@@ -17084,7 +17044,7 @@
         <v>46213.75945601852</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>106</v>
@@ -17128,7 +17088,7 @@
         <v>46213.75945601852</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>106</v>
@@ -17172,7 +17132,7 @@
         <v>46213.75945601852</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>106</v>
@@ -17216,7 +17176,7 @@
         <v>46213.75945601852</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>106</v>
@@ -17260,7 +17220,7 @@
         <v>46213.75945601852</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>106</v>
@@ -17304,7 +17264,7 @@
         <v>46213.75945601852</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>106</v>
@@ -17348,7 +17308,7 @@
         <v>46213.75945601852</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>106</v>
@@ -17384,6 +17344,3130 @@
         <v>6.0</v>
       </c>
       <c r="O364" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2">
+        <v>46218.5408912037</v>
+      </c>
+      <c r="B365" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C365" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D365" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E365" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F365" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G365" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H365" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="J365" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K365" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L365" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M365" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N365" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O365" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2">
+        <v>46218.5408912037</v>
+      </c>
+      <c r="B366" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E366" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F366" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G366" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H366" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J366" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K366" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L366" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M366" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N366" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O366" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2">
+        <v>46218.5408912037</v>
+      </c>
+      <c r="B367" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C367" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E367" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F367" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G367" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H367" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J367" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K367" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L367" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M367" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N367" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O367" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2">
+        <v>46218.5408912037</v>
+      </c>
+      <c r="B368" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E368" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F368" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="G368" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H368" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J368" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K368" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L368" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M368" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N368" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O368" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2">
+        <v>46218.5408912037</v>
+      </c>
+      <c r="B369" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D369" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E369" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F369" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G369" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H369" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J369" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K369" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L369" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M369" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N369" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O369" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2">
+        <v>46218.5408912037</v>
+      </c>
+      <c r="B370" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D370" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E370" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="F370" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="G370" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="H370" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="J370" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K370" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L370" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M370" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N370" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O370" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2">
+        <v>46218.5408912037</v>
+      </c>
+      <c r="B371" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C371" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D371" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E371" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F371" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G371" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H371" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J371" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K371" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L371" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M371" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N371" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O371" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2">
+        <v>46218.5408912037</v>
+      </c>
+      <c r="B372" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D372" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E372" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="F372" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G372" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H372" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J372" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K372" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L372" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M372" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N372" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O372" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2">
+        <v>46218.5408912037</v>
+      </c>
+      <c r="B373" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C373" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D373" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E373" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F373" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G373" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H373" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J373" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K373" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L373" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M373" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N373" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O373" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2">
+        <v>46218.5408912037</v>
+      </c>
+      <c r="B374" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D374" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E374" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="F374" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G374" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="H374" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="J374" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K374" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L374" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M374" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N374" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O374" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2">
+        <v>46218.5408912037</v>
+      </c>
+      <c r="B375" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C375" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D375" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E375" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="F375" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G375" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="H375" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="J375" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K375" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L375" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M375" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N375" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O375" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2">
+        <v>46218.5408912037</v>
+      </c>
+      <c r="B376" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C376" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D376" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E376" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="F376" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G376" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="H376" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="J376" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K376" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L376" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M376" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N376" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O376" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2">
+        <v>46218.5408912037</v>
+      </c>
+      <c r="B377" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C377" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D377" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E377" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F377" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G377" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H377" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J377" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K377" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L377" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M377" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N377" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O377" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2">
+        <v>46218.54195601852</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D378" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E378" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="F378" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G378" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H378" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J378" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="K378" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L378" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="M378" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N378" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="O378" s="3">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2">
+        <v>46218.56349537037</v>
+      </c>
+      <c r="B379" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C379" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D379" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E379" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F379" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G379" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H379" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J379" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="K379" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="L379" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M379" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N379" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O379" s="3">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2">
+        <v>46218.56349537037</v>
+      </c>
+      <c r="B380" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C380" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D380" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E380" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="F380" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G380" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H380" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J380" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="K380" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="L380" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M380" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N380" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O380" s="3">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2">
+        <v>46218.56349537037</v>
+      </c>
+      <c r="B381" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C381" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D381" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E381" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F381" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G381" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H381" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J381" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="K381" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="L381" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M381" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N381" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O381" s="3">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2">
+        <v>46218.56349537037</v>
+      </c>
+      <c r="B382" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C382" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D382" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E382" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="F382" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G382" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H382" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J382" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="K382" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="L382" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M382" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N382" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O382" s="3">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2">
+        <v>46218.56349537037</v>
+      </c>
+      <c r="B383" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C383" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D383" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E383" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="F383" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G383" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="H383" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="J383" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="K383" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="L383" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M383" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N383" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O383" s="3">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2">
+        <v>46218.56349537037</v>
+      </c>
+      <c r="B384" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C384" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D384" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E384" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F384" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G384" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H384" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J384" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="K384" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="L384" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M384" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N384" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O384" s="3">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2">
+        <v>46218.56349537037</v>
+      </c>
+      <c r="B385" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C385" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D385" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E385" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="F385" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G385" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="H385" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="J385" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="K385" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="L385" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M385" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N385" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O385" s="3">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2">
+        <v>46218.56349537037</v>
+      </c>
+      <c r="B386" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C386" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D386" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E386" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="F386" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G386" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H386" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="J386" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="K386" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="L386" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M386" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N386" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O386" s="3">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2">
+        <v>46218.56349537037</v>
+      </c>
+      <c r="B387" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C387" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D387" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E387" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="F387" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G387" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="H387" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="J387" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="K387" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="L387" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M387" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N387" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O387" s="3">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2">
+        <v>46218.56349537037</v>
+      </c>
+      <c r="B388" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C388" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D388" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E388" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="F388" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G388" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="H388" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="J388" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="K388" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="L388" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M388" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N388" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O388" s="3">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2">
+        <v>46218.56349537037</v>
+      </c>
+      <c r="B389" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C389" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D389" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E389" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="F389" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G389" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H389" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J389" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="K389" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="L389" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M389" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N389" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O389" s="3">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2">
+        <v>46218.56349537037</v>
+      </c>
+      <c r="B390" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C390" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D390" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E390" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F390" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G390" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H390" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J390" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="K390" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="L390" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M390" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N390" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O390" s="3">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2">
+        <v>46218.59045138889</v>
+      </c>
+      <c r="B391" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C391" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D391" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E391" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F391" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G391" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H391" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="J391" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K391" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L391" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M391" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N391" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O391" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2">
+        <v>46218.59045138889</v>
+      </c>
+      <c r="B392" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C392" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D392" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E392" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F392" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G392" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H392" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J392" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K392" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L392" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M392" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N392" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O392" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2">
+        <v>46218.59045138889</v>
+      </c>
+      <c r="B393" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C393" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D393" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E393" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F393" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="G393" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H393" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J393" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K393" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L393" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M393" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N393" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O393" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2">
+        <v>46218.59045138889</v>
+      </c>
+      <c r="B394" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C394" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D394" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E394" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F394" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="G394" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H394" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J394" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K394" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L394" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M394" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N394" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O394" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2">
+        <v>46218.59045138889</v>
+      </c>
+      <c r="B395" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C395" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D395" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E395" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="F395" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G395" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H395" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="J395" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K395" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L395" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M395" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N395" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O395" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2">
+        <v>46218.59045138889</v>
+      </c>
+      <c r="B396" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D396" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E396" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="F396" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G396" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H396" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J396" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K396" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L396" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M396" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N396" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O396" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2">
+        <v>46218.59045138889</v>
+      </c>
+      <c r="B397" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C397" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D397" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E397" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="F397" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G397" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H397" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="J397" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K397" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L397" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M397" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N397" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O397" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2">
+        <v>46218.59045138889</v>
+      </c>
+      <c r="B398" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D398" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E398" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="F398" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G398" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="H398" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="J398" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K398" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L398" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M398" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N398" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O398" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2">
+        <v>46218.59045138889</v>
+      </c>
+      <c r="B399" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C399" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D399" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E399" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="F399" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G399" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H399" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J399" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K399" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L399" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M399" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N399" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O399" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2">
+        <v>46218.59045138889</v>
+      </c>
+      <c r="B400" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C400" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D400" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E400" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="F400" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G400" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H400" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J400" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K400" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L400" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M400" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N400" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O400" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2">
+        <v>46218.59045138889</v>
+      </c>
+      <c r="B401" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C401" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D401" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E401" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="F401" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G401" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H401" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J401" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K401" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L401" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M401" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N401" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O401" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2">
+        <v>46218.59045138889</v>
+      </c>
+      <c r="B402" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C402" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D402" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E402" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F402" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G402" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H402" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J402" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K402" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L402" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M402" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N402" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O402" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2">
+        <v>46218.59045138889</v>
+      </c>
+      <c r="B403" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C403" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D403" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E403" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F403" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G403" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H403" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J403" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K403" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L403" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M403" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N403" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O403" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2">
+        <v>46218.59045138889</v>
+      </c>
+      <c r="B404" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D404" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E404" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F404" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G404" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H404" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J404" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K404" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L404" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M404" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N404" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O404" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2">
+        <v>46218.59045138889</v>
+      </c>
+      <c r="B405" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C405" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D405" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E405" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F405" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G405" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H405" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J405" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K405" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L405" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M405" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N405" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O405" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2">
+        <v>46218.59202546296</v>
+      </c>
+      <c r="B406" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C406" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D406" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E406" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="F406" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G406" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="H406" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="J406" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K406" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L406" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M406" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N406" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O406" s="3">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2">
+        <v>46218.59202546296</v>
+      </c>
+      <c r="B407" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D407" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E407" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F407" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G407" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H407" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="J407" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K407" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L407" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M407" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N407" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O407" s="3">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2">
+        <v>46218.59202546296</v>
+      </c>
+      <c r="B408" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C408" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D408" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E408" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="F408" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G408" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="H408" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="J408" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K408" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L408" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M408" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N408" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O408" s="3">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2">
+        <v>46218.59202546296</v>
+      </c>
+      <c r="B409" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C409" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D409" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E409" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="F409" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G409" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H409" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="J409" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K409" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L409" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M409" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N409" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O409" s="3">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2">
+        <v>46218.59202546296</v>
+      </c>
+      <c r="B410" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C410" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D410" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E410" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="F410" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G410" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H410" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="J410" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K410" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L410" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M410" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N410" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O410" s="3">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2">
+        <v>46218.59202546296</v>
+      </c>
+      <c r="B411" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C411" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D411" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E411" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="F411" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G411" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H411" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="J411" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K411" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L411" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M411" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N411" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O411" s="3">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2">
+        <v>46218.59202546296</v>
+      </c>
+      <c r="B412" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C412" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D412" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E412" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="F412" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G412" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H412" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J412" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K412" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L412" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M412" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N412" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O412" s="3">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2">
+        <v>46218.59202546296</v>
+      </c>
+      <c r="B413" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C413" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D413" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E413" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="F413" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G413" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="H413" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="J413" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K413" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L413" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M413" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N413" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O413" s="3">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2">
+        <v>46218.59202546296</v>
+      </c>
+      <c r="B414" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C414" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D414" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E414" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="F414" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G414" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="H414" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="J414" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K414" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L414" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M414" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N414" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O414" s="3">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2">
+        <v>46218.59202546296</v>
+      </c>
+      <c r="B415" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C415" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D415" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E415" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="F415" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G415" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H415" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="J415" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K415" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L415" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M415" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N415" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O415" s="3">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2">
+        <v>46218.59202546296</v>
+      </c>
+      <c r="B416" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C416" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D416" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E416" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="F416" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G416" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H416" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="J416" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K416" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L416" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M416" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N416" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O416" s="3">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2">
+        <v>46218.59258101852</v>
+      </c>
+      <c r="B417" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C417" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D417" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E417" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="F417" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G417" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="H417" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="J417" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K417" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L417" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M417" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N417" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O417" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2">
+        <v>46218.59258101852</v>
+      </c>
+      <c r="B418" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C418" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E418" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F418" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G418" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H418" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J418" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K418" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L418" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M418" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N418" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O418" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2">
+        <v>46218.59258101852</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C419" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D419" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E419" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F419" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G419" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H419" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J419" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="K419" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L419" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="M419" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N419" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="O419" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2">
+        <v>46218.59284722222</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C420" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D420" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E420" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F420" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G420" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H420" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J420" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K420" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L420" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="M420" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N420" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="O420" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2">
+        <v>46218.59324074074</v>
+      </c>
+      <c r="B421" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C421" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D421" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E421" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F421" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G421" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H421" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J421" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K421" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L421" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="M421" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N421" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="O421" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2">
+        <v>46218.59324074074</v>
+      </c>
+      <c r="B422" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C422" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D422" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E422" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F422" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G422" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H422" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J422" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K422" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L422" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="M422" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N422" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="O422" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2">
+        <v>46218.59369212963</v>
+      </c>
+      <c r="B423" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C423" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D423" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E423" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F423" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G423" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H423" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J423" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K423" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L423" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="M423" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N423" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="O423" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2">
+        <v>46218.59369212963</v>
+      </c>
+      <c r="B424" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C424" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D424" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E424" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F424" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G424" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H424" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J424" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K424" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L424" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="M424" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N424" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="O424" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2">
+        <v>46218.59369212963</v>
+      </c>
+      <c r="B425" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C425" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D425" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E425" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F425" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G425" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H425" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J425" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K425" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L425" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="M425" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N425" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="O425" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2">
+        <v>46218.59369212963</v>
+      </c>
+      <c r="B426" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C426" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D426" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E426" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F426" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G426" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H426" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J426" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K426" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L426" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="M426" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N426" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="O426" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2">
+        <v>46218.59457175926</v>
+      </c>
+      <c r="B427" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C427" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D427" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E427" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="F427" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G427" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H427" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J427" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="K427" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="L427" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M427" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N427" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="O427" s="3">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2">
+        <v>46218.59457175926</v>
+      </c>
+      <c r="B428" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C428" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D428" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E428" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="F428" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G428" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H428" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J428" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="K428" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="L428" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M428" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N428" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="O428" s="3">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2">
+        <v>46218.59457175926</v>
+      </c>
+      <c r="B429" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C429" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D429" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E429" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="F429" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G429" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H429" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J429" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="K429" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="L429" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="M429" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N429" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="O429" s="3">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2">
+        <v>46218.59510416666</v>
+      </c>
+      <c r="B430" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C430" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D430" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E430" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F430" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G430" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H430" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J430" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K430" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L430" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="M430" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N430" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="O430" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2">
+        <v>46218.59510416666</v>
+      </c>
+      <c r="B431" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C431" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D431" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E431" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F431" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G431" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H431" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J431" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K431" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L431" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="M431" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N431" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="O431" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2">
+        <v>46218.59510416666</v>
+      </c>
+      <c r="B432" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C432" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D432" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E432" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F432" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G432" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H432" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J432" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K432" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L432" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="M432" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N432" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="O432" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2">
+        <v>46218.59510416666</v>
+      </c>
+      <c r="B433" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C433" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D433" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E433" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F433" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G433" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H433" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J433" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K433" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L433" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="M433" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N433" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="O433" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2">
+        <v>46218.59510416666</v>
+      </c>
+      <c r="B434" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C434" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D434" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E434" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F434" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G434" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H434" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J434" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K434" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L434" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="M434" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N434" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="O434" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2">
+        <v>46218.59510416666</v>
+      </c>
+      <c r="B435" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C435" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D435" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E435" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F435" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G435" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H435" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J435" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K435" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L435" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="M435" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N435" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="O435" s="3">
         <v>5.0</v>
       </c>
     </row>
